--- a/artfynd/A 29467-2025 artfynd.xlsx
+++ b/artfynd/A 29467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120317912</v>
+        <v>120317906</v>
       </c>
       <c r="B2" t="n">
-        <v>91895</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6055</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572014</v>
+        <v>571945</v>
       </c>
       <c r="R2" t="n">
-        <v>6961630</v>
+        <v>6961923</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120317906</v>
+        <v>120317917</v>
       </c>
       <c r="B3" t="n">
-        <v>78207</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571945</v>
+        <v>572037</v>
       </c>
       <c r="R3" t="n">
-        <v>6961923</v>
+        <v>6961521</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120317909</v>
+        <v>120317902</v>
       </c>
       <c r="B4" t="n">
-        <v>91911</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571943</v>
+        <v>571944</v>
       </c>
       <c r="R4" t="n">
-        <v>6961899</v>
+        <v>6961926</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120317911</v>
+        <v>120317916</v>
       </c>
       <c r="B5" t="n">
-        <v>91923</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572109</v>
+        <v>572120</v>
       </c>
       <c r="R5" t="n">
-        <v>6961741</v>
+        <v>6961574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120317902</v>
+        <v>120317908</v>
       </c>
       <c r="B6" t="n">
-        <v>89696</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571944</v>
+        <v>571947</v>
       </c>
       <c r="R6" t="n">
-        <v>6961926</v>
+        <v>6961906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120317914</v>
+        <v>120317913</v>
       </c>
       <c r="B7" t="n">
-        <v>91911</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572026</v>
+        <v>572024</v>
       </c>
       <c r="R7" t="n">
-        <v>6961615</v>
+        <v>6961610</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120317913</v>
+        <v>120317909</v>
       </c>
       <c r="B8" t="n">
-        <v>91905</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572024</v>
+        <v>571943</v>
       </c>
       <c r="R8" t="n">
-        <v>6961610</v>
+        <v>6961899</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120317905</v>
+        <v>120317914</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571946</v>
+        <v>572026</v>
       </c>
       <c r="R9" t="n">
-        <v>6961924</v>
+        <v>6961615</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120317916</v>
+        <v>120317911</v>
       </c>
       <c r="B10" t="n">
-        <v>95300</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572120</v>
+        <v>572109</v>
       </c>
       <c r="R10" t="n">
-        <v>6961574</v>
+        <v>6961741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120317904</v>
+        <v>120317905</v>
       </c>
       <c r="B11" t="n">
-        <v>77946</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,7 +1583,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571945</v>
+        <v>571946</v>
       </c>
       <c r="R11" t="n">
         <v>6961924</v>
@@ -1695,53 +1645,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120317918</v>
+        <v>120317907</v>
       </c>
       <c r="B12" t="n">
-        <v>105107</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>6006</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Oljeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sistotrema alboluteum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oppsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571979</v>
+        <v>571945</v>
       </c>
       <c r="R12" t="n">
-        <v>6961524</v>
+        <v>6961906</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1779,6 +1727,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1797,37 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120317901</v>
+        <v>120317912</v>
       </c>
       <c r="B13" t="n">
-        <v>79151</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1781,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571944</v>
+        <v>572014</v>
       </c>
       <c r="R13" t="n">
-        <v>6961928</v>
+        <v>6961630</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,16 +1846,11 @@
         <v>120317910</v>
       </c>
       <c r="B14" t="n">
-        <v>78562</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2001,15 +1940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120317915</v>
+        <v>120317904</v>
       </c>
       <c r="B15" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1951,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +1975,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572104</v>
+        <v>571945</v>
       </c>
       <c r="R15" t="n">
-        <v>6961573</v>
+        <v>6961924</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,37 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120317917</v>
+        <v>120317918</v>
       </c>
       <c r="B16" t="n">
-        <v>90636</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,13 +2072,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572037</v>
+        <v>571979</v>
       </c>
       <c r="R16" t="n">
-        <v>6961521</v>
+        <v>6961524</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2205,15 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120317908</v>
+        <v>120317901</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571947</v>
+        <v>571944</v>
       </c>
       <c r="R17" t="n">
-        <v>6961906</v>
+        <v>6961928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,112 +2228,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>120317907</v>
-      </c>
-      <c r="B18" t="n">
-        <v>90489</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DD</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6006</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Oljeporing</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Sistotrema alboluteum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Oppsjöflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>571945</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6961906</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
